--- a/Codelist Excel Files and Conversion Templates to XML/platformType.xlsx
+++ b/Codelist Excel Files and Conversion Templates to XML/platformType.xlsx
@@ -1119,7 +1119,7 @@
       </c>
       <c r="D3" s="14" t="inlineStr">
         <is>
-          <t>A granular fill platform reinforced with one or more geogrid or geotextile layers. Recorded here as an explicit classification even though it is also derivable from whether diggs:LoadTransferPlatformType/geosynthetics (as-built) or diggs:GeosyntheticLayerDesign (design) is populated - stating it directly lets a reviewer read the platform's construction type from one field rather than checking for the presence of a child array.</t>
+          <t>A granular fill platform reinforced with one or more geogrid or geotextile layers. Recorded here as an explicit classification even though it is also derivable from whether diggs:LoadTransferPlatformType/geosynthetics (as-built) or diggs:DesignGeosyntheticLayer (design) is populated - stating it directly lets a reviewer read the platform's construction type from one field rather than checking for the presence of a child array.</t>
         </is>
       </c>
       <c r="E3" s="13" t="inlineStr">
